--- a/8-repetition/latin_square.xlsx
+++ b/8-repetition/latin_square.xlsx
@@ -5,20 +5,31 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/433d595d6ddc6943/Desktop/Projects/Factorial_satiation/8-repetition/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aldos\OneDrive\Desktop\Projects\Factorial_satiation\8-repetition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F25DC773A252ABDACC10485FB1995AD05ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45A6986C-4D0D-4424-9FA5-29E74DBB4A38}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E524D06-041A-407D-88C2-8EA971AEB596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -749,17 +760,17 @@
       <c r="E11" s="10">
         <v>9724</v>
       </c>
-      <c r="F11">
-        <v>9518</v>
-      </c>
-      <c r="G11">
-        <v>9415</v>
-      </c>
-      <c r="H11">
-        <v>9726</v>
-      </c>
-      <c r="I11">
-        <v>9427</v>
+      <c r="F11" s="10">
+        <v>9514</v>
+      </c>
+      <c r="G11" s="7">
+        <v>9411</v>
+      </c>
+      <c r="H11" s="8">
+        <v>9722</v>
+      </c>
+      <c r="I11" s="9">
+        <v>9423</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -778,17 +789,17 @@
       <c r="E12" s="10">
         <v>9324</v>
       </c>
-      <c r="F12">
-        <v>324</v>
-      </c>
-      <c r="G12">
-        <v>9725</v>
-      </c>
-      <c r="H12">
-        <v>242</v>
-      </c>
-      <c r="I12">
-        <v>283</v>
+      <c r="F12" s="10">
+        <v>164</v>
+      </c>
+      <c r="G12" s="7">
+        <v>9721</v>
+      </c>
+      <c r="H12" s="8">
+        <v>82</v>
+      </c>
+      <c r="I12" s="9">
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -807,17 +818,17 @@
       <c r="E13" s="10">
         <v>134</v>
       </c>
-      <c r="F13">
-        <v>9128</v>
-      </c>
-      <c r="G13">
-        <v>201</v>
-      </c>
-      <c r="H13">
-        <v>9216</v>
-      </c>
-      <c r="I13">
-        <v>9727</v>
+      <c r="F13" s="10">
+        <v>9124</v>
+      </c>
+      <c r="G13" s="7">
+        <v>41</v>
+      </c>
+      <c r="H13" s="8">
+        <v>9212</v>
+      </c>
+      <c r="I13" s="9">
+        <v>9723</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -836,17 +847,17 @@
       <c r="E14" s="10">
         <v>9424</v>
       </c>
-      <c r="F14">
-        <v>9318</v>
-      </c>
-      <c r="G14">
-        <v>9425</v>
-      </c>
-      <c r="H14">
-        <v>9426</v>
-      </c>
-      <c r="I14">
-        <v>9217</v>
+      <c r="F14" s="10">
+        <v>9314</v>
+      </c>
+      <c r="G14" s="7">
+        <v>9421</v>
+      </c>
+      <c r="H14" s="8">
+        <v>9422</v>
+      </c>
+      <c r="I14" s="9">
+        <v>9213</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -865,17 +876,17 @@
       <c r="E15" s="10">
         <v>9214</v>
       </c>
-      <c r="F15">
-        <v>313</v>
-      </c>
-      <c r="G15">
-        <v>9315</v>
-      </c>
-      <c r="H15">
-        <v>231</v>
-      </c>
-      <c r="I15">
-        <v>9327</v>
+      <c r="F15" s="10">
+        <v>153</v>
+      </c>
+      <c r="G15" s="7">
+        <v>9311</v>
+      </c>
+      <c r="H15" s="8">
+        <v>71</v>
+      </c>
+      <c r="I15" s="9">
+        <v>9323</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -894,17 +905,17 @@
       <c r="E16" s="10">
         <v>141</v>
       </c>
-      <c r="F16">
-        <v>9418</v>
-      </c>
-      <c r="G16">
-        <v>194</v>
-      </c>
-      <c r="H16">
-        <v>9416</v>
-      </c>
-      <c r="I16">
-        <v>272</v>
+      <c r="F16" s="10">
+        <v>9414</v>
+      </c>
+      <c r="G16" s="7">
+        <v>34</v>
+      </c>
+      <c r="H16" s="8">
+        <v>9412</v>
+      </c>
+      <c r="I16" s="9">
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -923,17 +934,17 @@
       <c r="E17" s="10">
         <v>9714</v>
       </c>
-      <c r="F17">
-        <v>9118</v>
-      </c>
-      <c r="G17">
-        <v>9125</v>
-      </c>
-      <c r="H17">
-        <v>9126</v>
-      </c>
-      <c r="I17">
-        <v>9717</v>
+      <c r="F17" s="10">
+        <v>9114</v>
+      </c>
+      <c r="G17" s="7">
+        <v>9121</v>
+      </c>
+      <c r="H17" s="8">
+        <v>9122</v>
+      </c>
+      <c r="I17" s="9">
+        <v>9713</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -952,17 +963,17 @@
       <c r="E18" s="10">
         <v>9114</v>
       </c>
-      <c r="F18">
-        <v>9718</v>
-      </c>
-      <c r="G18">
-        <v>9325</v>
-      </c>
-      <c r="H18">
-        <v>9326</v>
-      </c>
-      <c r="I18">
-        <v>9417</v>
+      <c r="F18" s="10">
+        <v>9714</v>
+      </c>
+      <c r="G18" s="7">
+        <v>9321</v>
+      </c>
+      <c r="H18" s="8">
+        <v>9322</v>
+      </c>
+      <c r="I18" s="9">
+        <v>9413</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -981,17 +992,17 @@
       <c r="E19" s="10">
         <v>9414</v>
       </c>
-      <c r="F19">
-        <v>302</v>
-      </c>
-      <c r="G19">
-        <v>183</v>
-      </c>
-      <c r="H19">
-        <v>224</v>
-      </c>
-      <c r="I19">
-        <v>9317</v>
+      <c r="F19" s="10">
+        <v>142</v>
+      </c>
+      <c r="G19" s="7">
+        <v>23</v>
+      </c>
+      <c r="H19" s="8">
+        <v>64</v>
+      </c>
+      <c r="I19" s="9">
+        <v>9313</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1010,17 +1021,17 @@
       <c r="E20" s="10">
         <v>152</v>
       </c>
-      <c r="F20">
-        <v>9218</v>
-      </c>
-      <c r="G20">
-        <v>9715</v>
-      </c>
-      <c r="H20">
-        <v>9316</v>
-      </c>
-      <c r="I20">
-        <v>261</v>
+      <c r="F20" s="10">
+        <v>9214</v>
+      </c>
+      <c r="G20" s="7">
+        <v>9711</v>
+      </c>
+      <c r="H20" s="8">
+        <v>9312</v>
+      </c>
+      <c r="I20" s="9">
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1039,17 +1050,17 @@
       <c r="E21" s="10">
         <v>9314</v>
       </c>
-      <c r="F21">
-        <v>9428</v>
-      </c>
-      <c r="G21">
-        <v>9215</v>
-      </c>
-      <c r="H21">
-        <v>9116</v>
-      </c>
-      <c r="I21">
-        <v>9117</v>
+      <c r="F21" s="10">
+        <v>9424</v>
+      </c>
+      <c r="G21" s="7">
+        <v>9211</v>
+      </c>
+      <c r="H21" s="8">
+        <v>9112</v>
+      </c>
+      <c r="I21" s="9">
+        <v>9113</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1068,17 +1079,17 @@
       <c r="E22" s="10">
         <v>9124</v>
       </c>
-      <c r="F22">
-        <v>291</v>
-      </c>
-      <c r="G22">
-        <v>9515</v>
-      </c>
-      <c r="H22">
-        <v>9516</v>
-      </c>
-      <c r="I22">
-        <v>254</v>
+      <c r="F22" s="10">
+        <v>131</v>
+      </c>
+      <c r="G22" s="7">
+        <v>9511</v>
+      </c>
+      <c r="H22" s="8">
+        <v>9512</v>
+      </c>
+      <c r="I22" s="9">
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1097,17 +1108,17 @@
       <c r="E23" s="10">
         <v>163</v>
       </c>
-      <c r="F23">
-        <v>9328</v>
-      </c>
-      <c r="G23">
-        <v>172</v>
-      </c>
-      <c r="H23">
-        <v>213</v>
-      </c>
-      <c r="I23">
-        <v>9127</v>
+      <c r="F23" s="10">
+        <v>9324</v>
+      </c>
+      <c r="G23" s="7">
+        <v>12</v>
+      </c>
+      <c r="H23" s="8">
+        <v>53</v>
+      </c>
+      <c r="I23" s="9">
+        <v>9123</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1126,17 +1137,17 @@
       <c r="E24" s="10">
         <v>9514</v>
       </c>
-      <c r="F24">
-        <v>9728</v>
-      </c>
-      <c r="G24">
-        <v>9115</v>
-      </c>
-      <c r="H24">
-        <v>9716</v>
-      </c>
-      <c r="I24">
-        <v>9517</v>
+      <c r="F24" s="10">
+        <v>9724</v>
+      </c>
+      <c r="G24" s="7">
+        <v>9111</v>
+      </c>
+      <c r="H24" s="8">
+        <v>9712</v>
+      </c>
+      <c r="I24" s="9">
+        <v>9513</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1155,17 +1166,17 @@
       <c r="E25" s="7">
         <v>9111</v>
       </c>
-      <c r="F25">
-        <v>9427</v>
-      </c>
-      <c r="G25">
-        <v>9518</v>
-      </c>
-      <c r="H25">
-        <v>9415</v>
-      </c>
-      <c r="I25">
-        <v>9726</v>
+      <c r="F25" s="9">
+        <v>9423</v>
+      </c>
+      <c r="G25" s="10">
+        <v>9514</v>
+      </c>
+      <c r="H25" s="7">
+        <v>9411</v>
+      </c>
+      <c r="I25" s="8">
+        <v>9722</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1184,17 +1195,17 @@
       <c r="E26" s="7">
         <v>14</v>
       </c>
-      <c r="F26">
-        <v>284</v>
-      </c>
-      <c r="G26">
-        <v>321</v>
-      </c>
-      <c r="H26">
-        <v>9725</v>
-      </c>
-      <c r="I26">
-        <v>243</v>
+      <c r="F26" s="9">
+        <v>124</v>
+      </c>
+      <c r="G26" s="10">
+        <v>161</v>
+      </c>
+      <c r="H26" s="7">
+        <v>9721</v>
+      </c>
+      <c r="I26" s="8">
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1213,17 +1224,17 @@
       <c r="E27" s="7">
         <v>9511</v>
       </c>
-      <c r="F27">
-        <v>9727</v>
-      </c>
-      <c r="G27">
-        <v>9128</v>
-      </c>
-      <c r="H27">
-        <v>202</v>
-      </c>
-      <c r="I27">
-        <v>9216</v>
+      <c r="F27" s="9">
+        <v>9723</v>
+      </c>
+      <c r="G27" s="10">
+        <v>9124</v>
+      </c>
+      <c r="H27" s="7">
+        <v>42</v>
+      </c>
+      <c r="I27" s="8">
+        <v>9212</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1242,17 +1253,17 @@
       <c r="E28" s="7">
         <v>9211</v>
       </c>
-      <c r="F28">
-        <v>9217</v>
-      </c>
-      <c r="G28">
-        <v>9318</v>
-      </c>
-      <c r="H28">
-        <v>9425</v>
-      </c>
-      <c r="I28">
-        <v>9426</v>
+      <c r="F28" s="9">
+        <v>9213</v>
+      </c>
+      <c r="G28" s="10">
+        <v>9314</v>
+      </c>
+      <c r="H28" s="7">
+        <v>9421</v>
+      </c>
+      <c r="I28" s="8">
+        <v>9422</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1271,17 +1282,17 @@
       <c r="E29" s="7">
         <v>9711</v>
       </c>
-      <c r="F29">
-        <v>9327</v>
-      </c>
-      <c r="G29">
-        <v>314</v>
-      </c>
-      <c r="H29">
-        <v>9315</v>
-      </c>
-      <c r="I29">
-        <v>232</v>
+      <c r="F29" s="9">
+        <v>9323</v>
+      </c>
+      <c r="G29" s="10">
+        <v>154</v>
+      </c>
+      <c r="H29" s="7">
+        <v>9311</v>
+      </c>
+      <c r="I29" s="8">
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1300,17 +1311,17 @@
       <c r="E30" s="7">
         <v>21</v>
       </c>
-      <c r="F30">
-        <v>273</v>
-      </c>
-      <c r="G30">
-        <v>9418</v>
-      </c>
-      <c r="H30">
-        <v>191</v>
-      </c>
-      <c r="I30">
-        <v>9416</v>
+      <c r="F30" s="9">
+        <v>113</v>
+      </c>
+      <c r="G30" s="10">
+        <v>9414</v>
+      </c>
+      <c r="H30" s="7">
+        <v>31</v>
+      </c>
+      <c r="I30" s="8">
+        <v>9412</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1329,17 +1340,17 @@
       <c r="E31" s="7">
         <v>9321</v>
       </c>
-      <c r="F31">
-        <v>9717</v>
-      </c>
-      <c r="G31">
-        <v>9118</v>
-      </c>
-      <c r="H31">
-        <v>9125</v>
-      </c>
-      <c r="I31">
-        <v>9126</v>
+      <c r="F31" s="9">
+        <v>9713</v>
+      </c>
+      <c r="G31" s="10">
+        <v>9114</v>
+      </c>
+      <c r="H31" s="7">
+        <v>9121</v>
+      </c>
+      <c r="I31" s="8">
+        <v>9122</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1358,17 +1369,17 @@
       <c r="E32" s="7">
         <v>9121</v>
       </c>
-      <c r="F32">
-        <v>9417</v>
-      </c>
-      <c r="G32">
-        <v>9718</v>
-      </c>
-      <c r="H32">
-        <v>9325</v>
-      </c>
-      <c r="I32">
-        <v>9326</v>
+      <c r="F32" s="9">
+        <v>9413</v>
+      </c>
+      <c r="G32" s="10">
+        <v>9714</v>
+      </c>
+      <c r="H32" s="7">
+        <v>9321</v>
+      </c>
+      <c r="I32" s="8">
+        <v>9322</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1387,17 +1398,17 @@
       <c r="E33" s="7">
         <v>32</v>
       </c>
-      <c r="F33">
-        <v>9317</v>
-      </c>
-      <c r="G33">
-        <v>303</v>
-      </c>
-      <c r="H33">
-        <v>184</v>
-      </c>
-      <c r="I33">
-        <v>221</v>
+      <c r="F33" s="9">
+        <v>9313</v>
+      </c>
+      <c r="G33" s="10">
+        <v>143</v>
+      </c>
+      <c r="H33" s="7">
+        <v>24</v>
+      </c>
+      <c r="I33" s="8">
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1416,17 +1427,17 @@
       <c r="E34" s="7">
         <v>9311</v>
       </c>
-      <c r="F34">
-        <v>262</v>
-      </c>
-      <c r="G34">
-        <v>9218</v>
-      </c>
-      <c r="H34">
-        <v>9715</v>
-      </c>
-      <c r="I34">
-        <v>9316</v>
+      <c r="F34" s="9">
+        <v>102</v>
+      </c>
+      <c r="G34" s="10">
+        <v>9214</v>
+      </c>
+      <c r="H34" s="7">
+        <v>9711</v>
+      </c>
+      <c r="I34" s="8">
+        <v>9312</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1445,17 +1456,17 @@
       <c r="E35" s="7">
         <v>9421</v>
       </c>
-      <c r="F35">
-        <v>9117</v>
-      </c>
-      <c r="G35">
-        <v>9428</v>
-      </c>
-      <c r="H35">
-        <v>9215</v>
-      </c>
-      <c r="I35">
-        <v>9116</v>
+      <c r="F35" s="9">
+        <v>9113</v>
+      </c>
+      <c r="G35" s="10">
+        <v>9424</v>
+      </c>
+      <c r="H35" s="7">
+        <v>9211</v>
+      </c>
+      <c r="I35" s="8">
+        <v>9112</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1474,17 +1485,17 @@
       <c r="E36" s="7">
         <v>43</v>
       </c>
-      <c r="F36">
-        <v>251</v>
-      </c>
-      <c r="G36">
-        <v>292</v>
-      </c>
-      <c r="H36">
-        <v>9515</v>
-      </c>
-      <c r="I36">
-        <v>9516</v>
+      <c r="F36" s="9">
+        <v>91</v>
+      </c>
+      <c r="G36" s="10">
+        <v>132</v>
+      </c>
+      <c r="H36" s="7">
+        <v>9511</v>
+      </c>
+      <c r="I36" s="8">
+        <v>9512</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1503,17 +1514,17 @@
       <c r="E37" s="7">
         <v>9721</v>
       </c>
-      <c r="F37">
-        <v>9127</v>
-      </c>
-      <c r="G37">
-        <v>9328</v>
-      </c>
-      <c r="H37">
-        <v>173</v>
-      </c>
-      <c r="I37">
-        <v>214</v>
+      <c r="F37" s="9">
+        <v>9123</v>
+      </c>
+      <c r="G37" s="10">
+        <v>9324</v>
+      </c>
+      <c r="H37" s="7">
+        <v>13</v>
+      </c>
+      <c r="I37" s="8">
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1532,17 +1543,17 @@
       <c r="E38" s="7">
         <v>9411</v>
       </c>
-      <c r="F38">
-        <v>9517</v>
-      </c>
-      <c r="G38">
-        <v>9728</v>
-      </c>
-      <c r="H38">
-        <v>9115</v>
-      </c>
-      <c r="I38">
-        <v>9716</v>
+      <c r="F38" s="9">
+        <v>9513</v>
+      </c>
+      <c r="G38" s="10">
+        <v>9724</v>
+      </c>
+      <c r="H38" s="7">
+        <v>9111</v>
+      </c>
+      <c r="I38" s="8">
+        <v>9712</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1561,17 +1572,17 @@
       <c r="E39" s="8">
         <v>9712</v>
       </c>
-      <c r="F39">
-        <v>9726</v>
-      </c>
-      <c r="G39">
-        <v>9427</v>
-      </c>
-      <c r="H39">
-        <v>9518</v>
-      </c>
-      <c r="I39">
-        <v>9415</v>
+      <c r="F39" s="8">
+        <v>9722</v>
+      </c>
+      <c r="G39" s="9">
+        <v>9423</v>
+      </c>
+      <c r="H39" s="10">
+        <v>9514</v>
+      </c>
+      <c r="I39" s="7">
+        <v>9411</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1590,17 +1601,17 @@
       <c r="E40" s="8">
         <v>54</v>
       </c>
-      <c r="F40">
-        <v>244</v>
-      </c>
-      <c r="G40">
-        <v>281</v>
-      </c>
-      <c r="H40">
-        <v>322</v>
-      </c>
-      <c r="I40">
-        <v>9725</v>
+      <c r="F40" s="8">
+        <v>84</v>
+      </c>
+      <c r="G40" s="9">
+        <v>121</v>
+      </c>
+      <c r="H40" s="10">
+        <v>162</v>
+      </c>
+      <c r="I40" s="7">
+        <v>9721</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1619,17 +1630,17 @@
       <c r="E41" s="8">
         <v>9512</v>
       </c>
-      <c r="F41">
-        <v>9216</v>
-      </c>
-      <c r="G41">
-        <v>9727</v>
-      </c>
-      <c r="H41">
-        <v>9128</v>
-      </c>
-      <c r="I41">
-        <v>203</v>
+      <c r="F41" s="8">
+        <v>9212</v>
+      </c>
+      <c r="G41" s="9">
+        <v>9723</v>
+      </c>
+      <c r="H41" s="10">
+        <v>9124</v>
+      </c>
+      <c r="I41" s="7">
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1648,17 +1659,17 @@
       <c r="E42" s="8">
         <v>9112</v>
       </c>
-      <c r="F42">
-        <v>9426</v>
-      </c>
-      <c r="G42">
-        <v>9217</v>
-      </c>
-      <c r="H42">
-        <v>9318</v>
-      </c>
-      <c r="I42">
-        <v>9425</v>
+      <c r="F42" s="8">
+        <v>9422</v>
+      </c>
+      <c r="G42" s="9">
+        <v>9213</v>
+      </c>
+      <c r="H42" s="10">
+        <v>9314</v>
+      </c>
+      <c r="I42" s="7">
+        <v>9421</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1677,17 +1688,17 @@
       <c r="E43" s="8">
         <v>9312</v>
       </c>
-      <c r="F43">
-        <v>233</v>
-      </c>
-      <c r="G43">
-        <v>9327</v>
-      </c>
-      <c r="H43">
-        <v>311</v>
-      </c>
-      <c r="I43">
-        <v>9315</v>
+      <c r="F43" s="8">
+        <v>73</v>
+      </c>
+      <c r="G43" s="9">
+        <v>9323</v>
+      </c>
+      <c r="H43" s="10">
+        <v>151</v>
+      </c>
+      <c r="I43" s="7">
+        <v>9311</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1706,17 +1717,17 @@
       <c r="E44" s="8">
         <v>61</v>
       </c>
-      <c r="F44">
-        <v>9416</v>
-      </c>
-      <c r="G44">
-        <v>274</v>
-      </c>
-      <c r="H44">
-        <v>9418</v>
-      </c>
-      <c r="I44">
-        <v>192</v>
+      <c r="F44" s="8">
+        <v>9412</v>
+      </c>
+      <c r="G44" s="9">
+        <v>114</v>
+      </c>
+      <c r="H44" s="10">
+        <v>9414</v>
+      </c>
+      <c r="I44" s="7">
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -1735,17 +1746,17 @@
       <c r="E45" s="8">
         <v>9322</v>
       </c>
-      <c r="F45">
-        <v>9126</v>
-      </c>
-      <c r="G45">
-        <v>9717</v>
-      </c>
-      <c r="H45">
-        <v>9118</v>
-      </c>
-      <c r="I45">
-        <v>9125</v>
+      <c r="F45" s="8">
+        <v>9122</v>
+      </c>
+      <c r="G45" s="9">
+        <v>9713</v>
+      </c>
+      <c r="H45" s="10">
+        <v>9114</v>
+      </c>
+      <c r="I45" s="7">
+        <v>9121</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -1764,17 +1775,17 @@
       <c r="E46" s="8">
         <v>9122</v>
       </c>
-      <c r="F46">
-        <v>9326</v>
-      </c>
-      <c r="G46">
-        <v>9417</v>
-      </c>
-      <c r="H46">
-        <v>9718</v>
-      </c>
-      <c r="I46">
-        <v>9325</v>
+      <c r="F46" s="8">
+        <v>9322</v>
+      </c>
+      <c r="G46" s="9">
+        <v>9413</v>
+      </c>
+      <c r="H46" s="10">
+        <v>9714</v>
+      </c>
+      <c r="I46" s="7">
+        <v>9321</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -1793,17 +1804,17 @@
       <c r="E47" s="8">
         <v>9412</v>
       </c>
-      <c r="F47">
-        <v>222</v>
-      </c>
-      <c r="G47">
-        <v>9317</v>
-      </c>
-      <c r="H47">
-        <v>304</v>
-      </c>
-      <c r="I47">
-        <v>181</v>
+      <c r="F47" s="8">
+        <v>62</v>
+      </c>
+      <c r="G47" s="9">
+        <v>9313</v>
+      </c>
+      <c r="H47" s="10">
+        <v>144</v>
+      </c>
+      <c r="I47" s="7">
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -1822,17 +1833,17 @@
       <c r="E48" s="8">
         <v>72</v>
       </c>
-      <c r="F48">
-        <v>9316</v>
-      </c>
-      <c r="G48">
-        <v>263</v>
-      </c>
-      <c r="H48">
-        <v>9218</v>
-      </c>
-      <c r="I48">
-        <v>9715</v>
+      <c r="F48" s="8">
+        <v>9312</v>
+      </c>
+      <c r="G48" s="9">
+        <v>103</v>
+      </c>
+      <c r="H48" s="10">
+        <v>9214</v>
+      </c>
+      <c r="I48" s="7">
+        <v>9711</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -1851,17 +1862,17 @@
       <c r="E49" s="8">
         <v>9422</v>
       </c>
-      <c r="F49">
-        <v>9116</v>
-      </c>
-      <c r="G49">
-        <v>9117</v>
-      </c>
-      <c r="H49">
-        <v>9428</v>
-      </c>
-      <c r="I49">
-        <v>9215</v>
+      <c r="F49" s="8">
+        <v>9112</v>
+      </c>
+      <c r="G49" s="9">
+        <v>9113</v>
+      </c>
+      <c r="H49" s="10">
+        <v>9424</v>
+      </c>
+      <c r="I49" s="7">
+        <v>9211</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -1880,17 +1891,17 @@
       <c r="E50" s="8">
         <v>9212</v>
       </c>
-      <c r="F50">
-        <v>9516</v>
-      </c>
-      <c r="G50">
-        <v>252</v>
-      </c>
-      <c r="H50">
-        <v>293</v>
-      </c>
-      <c r="I50">
-        <v>9515</v>
+      <c r="F50" s="8">
+        <v>9512</v>
+      </c>
+      <c r="G50" s="9">
+        <v>92</v>
+      </c>
+      <c r="H50" s="10">
+        <v>133</v>
+      </c>
+      <c r="I50" s="7">
+        <v>9511</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -1909,17 +1920,17 @@
       <c r="E51" s="8">
         <v>83</v>
       </c>
-      <c r="F51">
-        <v>211</v>
-      </c>
-      <c r="G51">
-        <v>9127</v>
-      </c>
-      <c r="H51">
-        <v>9328</v>
-      </c>
-      <c r="I51">
-        <v>174</v>
+      <c r="F51" s="8">
+        <v>51</v>
+      </c>
+      <c r="G51" s="9">
+        <v>9123</v>
+      </c>
+      <c r="H51" s="10">
+        <v>9324</v>
+      </c>
+      <c r="I51" s="7">
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -1938,17 +1949,17 @@
       <c r="E52" s="8">
         <v>9722</v>
       </c>
-      <c r="F52">
-        <v>9716</v>
-      </c>
-      <c r="G52">
-        <v>9517</v>
-      </c>
-      <c r="H52">
-        <v>9728</v>
-      </c>
-      <c r="I52">
-        <v>9115</v>
+      <c r="F52" s="8">
+        <v>9712</v>
+      </c>
+      <c r="G52" s="9">
+        <v>9513</v>
+      </c>
+      <c r="H52" s="10">
+        <v>9724</v>
+      </c>
+      <c r="I52" s="7">
+        <v>9111</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -1967,17 +1978,17 @@
       <c r="E53" s="9">
         <v>9513</v>
       </c>
-      <c r="F53">
-        <v>9415</v>
-      </c>
-      <c r="G53">
-        <v>9726</v>
-      </c>
-      <c r="H53">
-        <v>9427</v>
-      </c>
-      <c r="I53">
-        <v>9518</v>
+      <c r="F53" s="7">
+        <v>9411</v>
+      </c>
+      <c r="G53" s="8">
+        <v>9722</v>
+      </c>
+      <c r="H53" s="9">
+        <v>9423</v>
+      </c>
+      <c r="I53" s="10">
+        <v>9514</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -1996,17 +2007,17 @@
       <c r="E54" s="9">
         <v>9123</v>
       </c>
-      <c r="F54">
-        <v>9725</v>
-      </c>
-      <c r="G54">
-        <v>241</v>
-      </c>
-      <c r="H54">
-        <v>282</v>
-      </c>
-      <c r="I54">
-        <v>323</v>
+      <c r="F54" s="7">
+        <v>9721</v>
+      </c>
+      <c r="G54" s="8">
+        <v>81</v>
+      </c>
+      <c r="H54" s="9">
+        <v>122</v>
+      </c>
+      <c r="I54" s="10">
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2025,17 +2036,17 @@
       <c r="E55" s="9">
         <v>94</v>
       </c>
-      <c r="F55">
-        <v>204</v>
-      </c>
-      <c r="G55">
-        <v>9216</v>
-      </c>
-      <c r="H55">
-        <v>9727</v>
-      </c>
-      <c r="I55">
-        <v>9128</v>
+      <c r="F55" s="7">
+        <v>44</v>
+      </c>
+      <c r="G55" s="8">
+        <v>9212</v>
+      </c>
+      <c r="H55" s="9">
+        <v>9723</v>
+      </c>
+      <c r="I55" s="10">
+        <v>9124</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2054,17 +2065,17 @@
       <c r="E56" s="9">
         <v>9113</v>
       </c>
-      <c r="F56">
-        <v>9425</v>
-      </c>
-      <c r="G56">
-        <v>9426</v>
-      </c>
-      <c r="H56">
-        <v>9217</v>
-      </c>
-      <c r="I56">
-        <v>9318</v>
+      <c r="F56" s="7">
+        <v>9421</v>
+      </c>
+      <c r="G56" s="8">
+        <v>9422</v>
+      </c>
+      <c r="H56" s="9">
+        <v>9213</v>
+      </c>
+      <c r="I56" s="10">
+        <v>9314</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2083,17 +2094,17 @@
       <c r="E57" s="9">
         <v>101</v>
       </c>
-      <c r="F57">
-        <v>9315</v>
-      </c>
-      <c r="G57">
-        <v>234</v>
-      </c>
-      <c r="H57">
-        <v>9327</v>
-      </c>
-      <c r="I57">
-        <v>312</v>
+      <c r="F57" s="7">
+        <v>9311</v>
+      </c>
+      <c r="G57" s="8">
+        <v>74</v>
+      </c>
+      <c r="H57" s="9">
+        <v>9323</v>
+      </c>
+      <c r="I57" s="10">
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2112,17 +2123,17 @@
       <c r="E58" s="9">
         <v>9313</v>
       </c>
-      <c r="F58">
-        <v>193</v>
-      </c>
-      <c r="G58">
-        <v>9416</v>
-      </c>
-      <c r="H58">
-        <v>271</v>
-      </c>
-      <c r="I58">
-        <v>9418</v>
+      <c r="F58" s="7">
+        <v>33</v>
+      </c>
+      <c r="G58" s="8">
+        <v>9412</v>
+      </c>
+      <c r="H58" s="9">
+        <v>111</v>
+      </c>
+      <c r="I58" s="10">
+        <v>9414</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2141,17 +2152,17 @@
       <c r="E59" s="9">
         <v>9413</v>
       </c>
-      <c r="F59">
-        <v>9125</v>
-      </c>
-      <c r="G59">
-        <v>9126</v>
-      </c>
-      <c r="H59">
-        <v>9717</v>
-      </c>
-      <c r="I59">
-        <v>9118</v>
+      <c r="F59" s="7">
+        <v>9121</v>
+      </c>
+      <c r="G59" s="8">
+        <v>9122</v>
+      </c>
+      <c r="H59" s="9">
+        <v>9713</v>
+      </c>
+      <c r="I59" s="10">
+        <v>9114</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2170,17 +2181,17 @@
       <c r="E60" s="9">
         <v>9713</v>
       </c>
-      <c r="F60">
-        <v>9325</v>
-      </c>
-      <c r="G60">
-        <v>9326</v>
-      </c>
-      <c r="H60">
-        <v>9417</v>
-      </c>
-      <c r="I60">
-        <v>9718</v>
+      <c r="F60" s="7">
+        <v>9321</v>
+      </c>
+      <c r="G60" s="8">
+        <v>9322</v>
+      </c>
+      <c r="H60" s="9">
+        <v>9413</v>
+      </c>
+      <c r="I60" s="10">
+        <v>9714</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -2199,17 +2210,17 @@
       <c r="E61" s="9">
         <v>112</v>
       </c>
-      <c r="F61">
-        <v>182</v>
-      </c>
-      <c r="G61">
-        <v>223</v>
-      </c>
-      <c r="H61">
-        <v>9317</v>
-      </c>
-      <c r="I61">
-        <v>301</v>
+      <c r="F61" s="7">
+        <v>22</v>
+      </c>
+      <c r="G61" s="8">
+        <v>63</v>
+      </c>
+      <c r="H61" s="9">
+        <v>9313</v>
+      </c>
+      <c r="I61" s="10">
+        <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2228,17 +2239,17 @@
       <c r="E62" s="9">
         <v>9323</v>
       </c>
-      <c r="F62">
-        <v>9715</v>
-      </c>
-      <c r="G62">
-        <v>9316</v>
-      </c>
-      <c r="H62">
-        <v>264</v>
-      </c>
-      <c r="I62">
-        <v>9218</v>
+      <c r="F62" s="7">
+        <v>9711</v>
+      </c>
+      <c r="G62" s="8">
+        <v>9312</v>
+      </c>
+      <c r="H62" s="9">
+        <v>104</v>
+      </c>
+      <c r="I62" s="10">
+        <v>9214</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2257,17 +2268,17 @@
       <c r="E63" s="9">
         <v>9213</v>
       </c>
-      <c r="F63">
-        <v>9215</v>
-      </c>
-      <c r="G63">
-        <v>9116</v>
-      </c>
-      <c r="H63">
-        <v>9117</v>
-      </c>
-      <c r="I63">
-        <v>9428</v>
+      <c r="F63" s="7">
+        <v>9211</v>
+      </c>
+      <c r="G63" s="8">
+        <v>9112</v>
+      </c>
+      <c r="H63" s="9">
+        <v>9113</v>
+      </c>
+      <c r="I63" s="10">
+        <v>9424</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2286,17 +2297,17 @@
       <c r="E64" s="9">
         <v>9723</v>
       </c>
-      <c r="F64">
-        <v>9515</v>
-      </c>
-      <c r="G64">
-        <v>9516</v>
-      </c>
-      <c r="H64">
-        <v>253</v>
-      </c>
-      <c r="I64">
-        <v>294</v>
+      <c r="F64" s="7">
+        <v>9511</v>
+      </c>
+      <c r="G64" s="8">
+        <v>9512</v>
+      </c>
+      <c r="H64" s="9">
+        <v>93</v>
+      </c>
+      <c r="I64" s="10">
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2315,17 +2326,17 @@
       <c r="E65" s="9">
         <v>123</v>
       </c>
-      <c r="F65">
-        <v>171</v>
-      </c>
-      <c r="G65">
-        <v>212</v>
-      </c>
-      <c r="H65">
-        <v>9127</v>
-      </c>
-      <c r="I65">
-        <v>9328</v>
+      <c r="F65" s="7">
+        <v>11</v>
+      </c>
+      <c r="G65" s="8">
+        <v>52</v>
+      </c>
+      <c r="H65" s="9">
+        <v>9123</v>
+      </c>
+      <c r="I65" s="10">
+        <v>9324</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2344,17 +2355,17 @@
       <c r="E66" s="9">
         <v>9423</v>
       </c>
-      <c r="F66">
-        <v>9115</v>
-      </c>
-      <c r="G66">
-        <v>9716</v>
-      </c>
-      <c r="H66">
-        <v>9517</v>
-      </c>
-      <c r="I66">
-        <v>9728</v>
+      <c r="F66" s="7">
+        <v>9111</v>
+      </c>
+      <c r="G66" s="8">
+        <v>9712</v>
+      </c>
+      <c r="H66" s="9">
+        <v>9513</v>
+      </c>
+      <c r="I66" s="10">
+        <v>9724</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2373,17 +2384,17 @@
       <c r="E67" s="10">
         <v>9728</v>
       </c>
-      <c r="F67">
-        <v>9514</v>
-      </c>
-      <c r="G67">
-        <v>9411</v>
-      </c>
-      <c r="H67">
-        <v>9722</v>
-      </c>
-      <c r="I67">
-        <v>9423</v>
+      <c r="F67" s="10">
+        <v>9518</v>
+      </c>
+      <c r="G67" s="7">
+        <v>9415</v>
+      </c>
+      <c r="H67" s="8">
+        <v>9726</v>
+      </c>
+      <c r="I67" s="9">
+        <v>9427</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2402,17 +2413,17 @@
       <c r="E68" s="10">
         <v>9328</v>
       </c>
-      <c r="F68">
-        <v>164</v>
-      </c>
-      <c r="G68">
-        <v>9721</v>
-      </c>
-      <c r="H68">
-        <v>82</v>
-      </c>
-      <c r="I68">
-        <v>123</v>
+      <c r="F68" s="10">
+        <v>324</v>
+      </c>
+      <c r="G68" s="7">
+        <v>9725</v>
+      </c>
+      <c r="H68" s="8">
+        <v>242</v>
+      </c>
+      <c r="I68" s="9">
+        <v>283</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2431,17 +2442,17 @@
       <c r="E69" s="10">
         <v>294</v>
       </c>
-      <c r="F69">
-        <v>9124</v>
-      </c>
-      <c r="G69">
-        <v>41</v>
-      </c>
-      <c r="H69">
-        <v>9212</v>
-      </c>
-      <c r="I69">
-        <v>9723</v>
+      <c r="F69" s="10">
+        <v>9128</v>
+      </c>
+      <c r="G69" s="7">
+        <v>201</v>
+      </c>
+      <c r="H69" s="8">
+        <v>9216</v>
+      </c>
+      <c r="I69" s="9">
+        <v>9727</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2460,17 +2471,17 @@
       <c r="E70" s="10">
         <v>9428</v>
       </c>
-      <c r="F70">
-        <v>9314</v>
-      </c>
-      <c r="G70">
-        <v>9421</v>
-      </c>
-      <c r="H70">
-        <v>9422</v>
-      </c>
-      <c r="I70">
-        <v>9213</v>
+      <c r="F70" s="10">
+        <v>9318</v>
+      </c>
+      <c r="G70" s="7">
+        <v>9425</v>
+      </c>
+      <c r="H70" s="8">
+        <v>9426</v>
+      </c>
+      <c r="I70" s="9">
+        <v>9217</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2489,17 +2500,17 @@
       <c r="E71" s="10">
         <v>9218</v>
       </c>
-      <c r="F71">
-        <v>153</v>
-      </c>
-      <c r="G71">
-        <v>9311</v>
-      </c>
-      <c r="H71">
-        <v>71</v>
-      </c>
-      <c r="I71">
-        <v>9323</v>
+      <c r="F71" s="10">
+        <v>313</v>
+      </c>
+      <c r="G71" s="7">
+        <v>9315</v>
+      </c>
+      <c r="H71" s="8">
+        <v>231</v>
+      </c>
+      <c r="I71" s="9">
+        <v>9327</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -2518,17 +2529,17 @@
       <c r="E72" s="10">
         <v>301</v>
       </c>
-      <c r="F72">
-        <v>9414</v>
-      </c>
-      <c r="G72">
-        <v>34</v>
-      </c>
-      <c r="H72">
-        <v>9412</v>
-      </c>
-      <c r="I72">
-        <v>112</v>
+      <c r="F72" s="10">
+        <v>9418</v>
+      </c>
+      <c r="G72" s="7">
+        <v>194</v>
+      </c>
+      <c r="H72" s="8">
+        <v>9416</v>
+      </c>
+      <c r="I72" s="9">
+        <v>272</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -2547,17 +2558,17 @@
       <c r="E73" s="10">
         <v>9718</v>
       </c>
-      <c r="F73">
-        <v>9114</v>
-      </c>
-      <c r="G73">
-        <v>9121</v>
-      </c>
-      <c r="H73">
-        <v>9122</v>
-      </c>
-      <c r="I73">
-        <v>9713</v>
+      <c r="F73" s="10">
+        <v>9118</v>
+      </c>
+      <c r="G73" s="7">
+        <v>9125</v>
+      </c>
+      <c r="H73" s="8">
+        <v>9126</v>
+      </c>
+      <c r="I73" s="9">
+        <v>9717</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -2576,17 +2587,17 @@
       <c r="E74" s="10">
         <v>9118</v>
       </c>
-      <c r="F74">
-        <v>9714</v>
-      </c>
-      <c r="G74">
-        <v>9321</v>
-      </c>
-      <c r="H74">
-        <v>9322</v>
-      </c>
-      <c r="I74">
-        <v>9413</v>
+      <c r="F74" s="10">
+        <v>9718</v>
+      </c>
+      <c r="G74" s="7">
+        <v>9325</v>
+      </c>
+      <c r="H74" s="8">
+        <v>9326</v>
+      </c>
+      <c r="I74" s="9">
+        <v>9417</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -2605,17 +2616,17 @@
       <c r="E75" s="10">
         <v>9418</v>
       </c>
-      <c r="F75">
-        <v>142</v>
-      </c>
-      <c r="G75">
-        <v>23</v>
-      </c>
-      <c r="H75">
-        <v>64</v>
-      </c>
-      <c r="I75">
-        <v>9313</v>
+      <c r="F75" s="10">
+        <v>302</v>
+      </c>
+      <c r="G75" s="7">
+        <v>183</v>
+      </c>
+      <c r="H75" s="8">
+        <v>224</v>
+      </c>
+      <c r="I75" s="9">
+        <v>9317</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -2634,17 +2645,17 @@
       <c r="E76" s="10">
         <v>312</v>
       </c>
-      <c r="F76">
-        <v>9214</v>
-      </c>
-      <c r="G76">
-        <v>9711</v>
-      </c>
-      <c r="H76">
-        <v>9312</v>
-      </c>
-      <c r="I76">
-        <v>101</v>
+      <c r="F76" s="10">
+        <v>9218</v>
+      </c>
+      <c r="G76" s="7">
+        <v>9715</v>
+      </c>
+      <c r="H76" s="8">
+        <v>9316</v>
+      </c>
+      <c r="I76" s="9">
+        <v>261</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -2663,17 +2674,17 @@
       <c r="E77" s="10">
         <v>9318</v>
       </c>
-      <c r="F77">
-        <v>9424</v>
-      </c>
-      <c r="G77">
-        <v>9211</v>
-      </c>
-      <c r="H77">
-        <v>9112</v>
-      </c>
-      <c r="I77">
-        <v>9113</v>
+      <c r="F77" s="10">
+        <v>9428</v>
+      </c>
+      <c r="G77" s="7">
+        <v>9215</v>
+      </c>
+      <c r="H77" s="8">
+        <v>9116</v>
+      </c>
+      <c r="I77" s="9">
+        <v>9117</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -2692,17 +2703,17 @@
       <c r="E78" s="10">
         <v>9128</v>
       </c>
-      <c r="F78">
-        <v>131</v>
-      </c>
-      <c r="G78">
-        <v>9511</v>
-      </c>
-      <c r="H78">
-        <v>9512</v>
-      </c>
-      <c r="I78">
-        <v>94</v>
+      <c r="F78" s="10">
+        <v>291</v>
+      </c>
+      <c r="G78" s="7">
+        <v>9515</v>
+      </c>
+      <c r="H78" s="8">
+        <v>9516</v>
+      </c>
+      <c r="I78" s="9">
+        <v>254</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -2721,17 +2732,17 @@
       <c r="E79" s="10">
         <v>323</v>
       </c>
-      <c r="F79">
-        <v>9324</v>
-      </c>
-      <c r="G79">
-        <v>12</v>
-      </c>
-      <c r="H79">
-        <v>53</v>
-      </c>
-      <c r="I79">
-        <v>9123</v>
+      <c r="F79" s="10">
+        <v>9328</v>
+      </c>
+      <c r="G79" s="7">
+        <v>172</v>
+      </c>
+      <c r="H79" s="8">
+        <v>213</v>
+      </c>
+      <c r="I79" s="9">
+        <v>9127</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -2750,17 +2761,17 @@
       <c r="E80" s="10">
         <v>9518</v>
       </c>
-      <c r="F80">
-        <v>9724</v>
-      </c>
-      <c r="G80">
-        <v>9111</v>
-      </c>
-      <c r="H80">
-        <v>9712</v>
-      </c>
-      <c r="I80">
-        <v>9513</v>
+      <c r="F80" s="10">
+        <v>9728</v>
+      </c>
+      <c r="G80" s="7">
+        <v>9115</v>
+      </c>
+      <c r="H80" s="8">
+        <v>9716</v>
+      </c>
+      <c r="I80" s="9">
+        <v>9517</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -2779,17 +2790,17 @@
       <c r="E81" s="7">
         <v>9115</v>
       </c>
-      <c r="F81">
-        <v>9423</v>
-      </c>
-      <c r="G81">
-        <v>9514</v>
-      </c>
-      <c r="H81">
-        <v>9411</v>
-      </c>
-      <c r="I81">
-        <v>9722</v>
+      <c r="F81" s="9">
+        <v>9427</v>
+      </c>
+      <c r="G81" s="10">
+        <v>9518</v>
+      </c>
+      <c r="H81" s="7">
+        <v>9415</v>
+      </c>
+      <c r="I81" s="8">
+        <v>9726</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -2808,17 +2819,17 @@
       <c r="E82" s="7">
         <v>174</v>
       </c>
-      <c r="F82">
-        <v>124</v>
-      </c>
-      <c r="G82">
-        <v>161</v>
-      </c>
-      <c r="H82">
-        <v>9721</v>
-      </c>
-      <c r="I82">
-        <v>83</v>
+      <c r="F82" s="9">
+        <v>284</v>
+      </c>
+      <c r="G82" s="10">
+        <v>321</v>
+      </c>
+      <c r="H82" s="7">
+        <v>9725</v>
+      </c>
+      <c r="I82" s="8">
+        <v>243</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -2837,17 +2848,17 @@
       <c r="E83" s="7">
         <v>9515</v>
       </c>
-      <c r="F83">
-        <v>9723</v>
-      </c>
-      <c r="G83">
-        <v>9124</v>
-      </c>
-      <c r="H83">
-        <v>42</v>
-      </c>
-      <c r="I83">
-        <v>9212</v>
+      <c r="F83" s="9">
+        <v>9727</v>
+      </c>
+      <c r="G83" s="10">
+        <v>9128</v>
+      </c>
+      <c r="H83" s="7">
+        <v>202</v>
+      </c>
+      <c r="I83" s="8">
+        <v>9216</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -2866,17 +2877,17 @@
       <c r="E84" s="7">
         <v>9215</v>
       </c>
-      <c r="F84">
-        <v>9213</v>
-      </c>
-      <c r="G84">
-        <v>9314</v>
-      </c>
-      <c r="H84">
-        <v>9421</v>
-      </c>
-      <c r="I84">
-        <v>9422</v>
+      <c r="F84" s="9">
+        <v>9217</v>
+      </c>
+      <c r="G84" s="10">
+        <v>9318</v>
+      </c>
+      <c r="H84" s="7">
+        <v>9425</v>
+      </c>
+      <c r="I84" s="8">
+        <v>9426</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -2895,17 +2906,17 @@
       <c r="E85" s="7">
         <v>9715</v>
       </c>
-      <c r="F85">
-        <v>9323</v>
-      </c>
-      <c r="G85">
-        <v>154</v>
-      </c>
-      <c r="H85">
-        <v>9311</v>
-      </c>
-      <c r="I85">
-        <v>72</v>
+      <c r="F85" s="9">
+        <v>9327</v>
+      </c>
+      <c r="G85" s="10">
+        <v>314</v>
+      </c>
+      <c r="H85" s="7">
+        <v>9315</v>
+      </c>
+      <c r="I85" s="8">
+        <v>232</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -2924,17 +2935,17 @@
       <c r="E86" s="7">
         <v>181</v>
       </c>
-      <c r="F86">
-        <v>113</v>
-      </c>
-      <c r="G86">
-        <v>9414</v>
-      </c>
-      <c r="H86">
-        <v>31</v>
-      </c>
-      <c r="I86">
-        <v>9412</v>
+      <c r="F86" s="9">
+        <v>273</v>
+      </c>
+      <c r="G86" s="10">
+        <v>9418</v>
+      </c>
+      <c r="H86" s="7">
+        <v>191</v>
+      </c>
+      <c r="I86" s="8">
+        <v>9416</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -2953,17 +2964,17 @@
       <c r="E87" s="7">
         <v>9325</v>
       </c>
-      <c r="F87">
-        <v>9713</v>
-      </c>
-      <c r="G87">
-        <v>9114</v>
-      </c>
-      <c r="H87">
-        <v>9121</v>
-      </c>
-      <c r="I87">
-        <v>9122</v>
+      <c r="F87" s="9">
+        <v>9717</v>
+      </c>
+      <c r="G87" s="10">
+        <v>9118</v>
+      </c>
+      <c r="H87" s="7">
+        <v>9125</v>
+      </c>
+      <c r="I87" s="8">
+        <v>9126</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -2982,17 +2993,17 @@
       <c r="E88" s="7">
         <v>9125</v>
       </c>
-      <c r="F88">
-        <v>9413</v>
-      </c>
-      <c r="G88">
-        <v>9714</v>
-      </c>
-      <c r="H88">
-        <v>9321</v>
-      </c>
-      <c r="I88">
-        <v>9322</v>
+      <c r="F88" s="9">
+        <v>9417</v>
+      </c>
+      <c r="G88" s="10">
+        <v>9718</v>
+      </c>
+      <c r="H88" s="7">
+        <v>9325</v>
+      </c>
+      <c r="I88" s="8">
+        <v>9326</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -3011,17 +3022,17 @@
       <c r="E89" s="7">
         <v>192</v>
       </c>
-      <c r="F89">
-        <v>9313</v>
-      </c>
-      <c r="G89">
-        <v>143</v>
-      </c>
-      <c r="H89">
-        <v>24</v>
-      </c>
-      <c r="I89">
-        <v>61</v>
+      <c r="F89" s="9">
+        <v>9317</v>
+      </c>
+      <c r="G89" s="10">
+        <v>303</v>
+      </c>
+      <c r="H89" s="7">
+        <v>184</v>
+      </c>
+      <c r="I89" s="8">
+        <v>221</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -3040,17 +3051,17 @@
       <c r="E90" s="7">
         <v>9315</v>
       </c>
-      <c r="F90">
-        <v>102</v>
-      </c>
-      <c r="G90">
-        <v>9214</v>
-      </c>
-      <c r="H90">
-        <v>9711</v>
-      </c>
-      <c r="I90">
-        <v>9312</v>
+      <c r="F90" s="9">
+        <v>262</v>
+      </c>
+      <c r="G90" s="10">
+        <v>9218</v>
+      </c>
+      <c r="H90" s="7">
+        <v>9715</v>
+      </c>
+      <c r="I90" s="8">
+        <v>9316</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -3069,17 +3080,17 @@
       <c r="E91" s="7">
         <v>9425</v>
       </c>
-      <c r="F91">
-        <v>9113</v>
-      </c>
-      <c r="G91">
-        <v>9424</v>
-      </c>
-      <c r="H91">
-        <v>9211</v>
-      </c>
-      <c r="I91">
-        <v>9112</v>
+      <c r="F91" s="9">
+        <v>9117</v>
+      </c>
+      <c r="G91" s="10">
+        <v>9428</v>
+      </c>
+      <c r="H91" s="7">
+        <v>9215</v>
+      </c>
+      <c r="I91" s="8">
+        <v>9116</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -3098,17 +3109,17 @@
       <c r="E92" s="7">
         <v>203</v>
       </c>
-      <c r="F92">
-        <v>91</v>
-      </c>
-      <c r="G92">
-        <v>132</v>
-      </c>
-      <c r="H92">
-        <v>9511</v>
-      </c>
-      <c r="I92">
-        <v>9512</v>
+      <c r="F92" s="9">
+        <v>251</v>
+      </c>
+      <c r="G92" s="10">
+        <v>292</v>
+      </c>
+      <c r="H92" s="7">
+        <v>9515</v>
+      </c>
+      <c r="I92" s="8">
+        <v>9516</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -3127,17 +3138,17 @@
       <c r="E93" s="7">
         <v>9725</v>
       </c>
-      <c r="F93">
-        <v>9123</v>
-      </c>
-      <c r="G93">
-        <v>9324</v>
-      </c>
-      <c r="H93">
-        <v>13</v>
-      </c>
-      <c r="I93">
-        <v>54</v>
+      <c r="F93" s="9">
+        <v>9127</v>
+      </c>
+      <c r="G93" s="10">
+        <v>9328</v>
+      </c>
+      <c r="H93" s="7">
+        <v>173</v>
+      </c>
+      <c r="I93" s="8">
+        <v>214</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -3156,17 +3167,17 @@
       <c r="E94" s="7">
         <v>9415</v>
       </c>
-      <c r="F94">
-        <v>9513</v>
-      </c>
-      <c r="G94">
-        <v>9724</v>
-      </c>
-      <c r="H94">
-        <v>9111</v>
-      </c>
-      <c r="I94">
-        <v>9712</v>
+      <c r="F94" s="9">
+        <v>9517</v>
+      </c>
+      <c r="G94" s="10">
+        <v>9728</v>
+      </c>
+      <c r="H94" s="7">
+        <v>9115</v>
+      </c>
+      <c r="I94" s="8">
+        <v>9716</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -3185,17 +3196,17 @@
       <c r="E95" s="8">
         <v>9716</v>
       </c>
-      <c r="F95">
-        <v>9722</v>
-      </c>
-      <c r="G95">
-        <v>9423</v>
-      </c>
-      <c r="H95">
-        <v>9514</v>
-      </c>
-      <c r="I95">
-        <v>9411</v>
+      <c r="F95" s="8">
+        <v>9726</v>
+      </c>
+      <c r="G95" s="9">
+        <v>9427</v>
+      </c>
+      <c r="H95" s="10">
+        <v>9518</v>
+      </c>
+      <c r="I95" s="7">
+        <v>9415</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -3214,17 +3225,17 @@
       <c r="E96" s="8">
         <v>214</v>
       </c>
-      <c r="F96">
-        <v>84</v>
-      </c>
-      <c r="G96">
-        <v>121</v>
-      </c>
-      <c r="H96">
-        <v>162</v>
-      </c>
-      <c r="I96">
-        <v>9721</v>
+      <c r="F96" s="8">
+        <v>244</v>
+      </c>
+      <c r="G96" s="9">
+        <v>281</v>
+      </c>
+      <c r="H96" s="10">
+        <v>322</v>
+      </c>
+      <c r="I96" s="7">
+        <v>9725</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -3243,17 +3254,17 @@
       <c r="E97" s="8">
         <v>9516</v>
       </c>
-      <c r="F97">
-        <v>9212</v>
-      </c>
-      <c r="G97">
-        <v>9723</v>
-      </c>
-      <c r="H97">
-        <v>9124</v>
-      </c>
-      <c r="I97">
-        <v>43</v>
+      <c r="F97" s="8">
+        <v>9216</v>
+      </c>
+      <c r="G97" s="9">
+        <v>9727</v>
+      </c>
+      <c r="H97" s="10">
+        <v>9128</v>
+      </c>
+      <c r="I97" s="7">
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -3272,17 +3283,17 @@
       <c r="E98" s="8">
         <v>9116</v>
       </c>
-      <c r="F98">
-        <v>9422</v>
-      </c>
-      <c r="G98">
-        <v>9213</v>
-      </c>
-      <c r="H98">
-        <v>9314</v>
-      </c>
-      <c r="I98">
-        <v>9421</v>
+      <c r="F98" s="8">
+        <v>9426</v>
+      </c>
+      <c r="G98" s="9">
+        <v>9217</v>
+      </c>
+      <c r="H98" s="10">
+        <v>9318</v>
+      </c>
+      <c r="I98" s="7">
+        <v>9425</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -3301,17 +3312,17 @@
       <c r="E99" s="8">
         <v>9316</v>
       </c>
-      <c r="F99">
-        <v>73</v>
-      </c>
-      <c r="G99">
-        <v>9323</v>
-      </c>
-      <c r="H99">
-        <v>151</v>
-      </c>
-      <c r="I99">
-        <v>9311</v>
+      <c r="F99" s="8">
+        <v>233</v>
+      </c>
+      <c r="G99" s="9">
+        <v>9327</v>
+      </c>
+      <c r="H99" s="10">
+        <v>311</v>
+      </c>
+      <c r="I99" s="7">
+        <v>9315</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -3330,17 +3341,17 @@
       <c r="E100" s="8">
         <v>221</v>
       </c>
-      <c r="F100">
-        <v>9412</v>
-      </c>
-      <c r="G100">
-        <v>114</v>
-      </c>
-      <c r="H100">
-        <v>9414</v>
-      </c>
-      <c r="I100">
-        <v>32</v>
+      <c r="F100" s="8">
+        <v>9416</v>
+      </c>
+      <c r="G100" s="9">
+        <v>274</v>
+      </c>
+      <c r="H100" s="10">
+        <v>9418</v>
+      </c>
+      <c r="I100" s="7">
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -3359,17 +3370,17 @@
       <c r="E101" s="8">
         <v>9326</v>
       </c>
-      <c r="F101">
-        <v>9122</v>
-      </c>
-      <c r="G101">
-        <v>9713</v>
-      </c>
-      <c r="H101">
-        <v>9114</v>
-      </c>
-      <c r="I101">
-        <v>9121</v>
+      <c r="F101" s="8">
+        <v>9126</v>
+      </c>
+      <c r="G101" s="9">
+        <v>9717</v>
+      </c>
+      <c r="H101" s="10">
+        <v>9118</v>
+      </c>
+      <c r="I101" s="7">
+        <v>9125</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -3388,17 +3399,17 @@
       <c r="E102" s="8">
         <v>9126</v>
       </c>
-      <c r="F102">
-        <v>9322</v>
-      </c>
-      <c r="G102">
-        <v>9413</v>
-      </c>
-      <c r="H102">
-        <v>9714</v>
-      </c>
-      <c r="I102">
-        <v>9321</v>
+      <c r="F102" s="8">
+        <v>9326</v>
+      </c>
+      <c r="G102" s="9">
+        <v>9417</v>
+      </c>
+      <c r="H102" s="10">
+        <v>9718</v>
+      </c>
+      <c r="I102" s="7">
+        <v>9325</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3417,17 +3428,17 @@
       <c r="E103" s="8">
         <v>9416</v>
       </c>
-      <c r="F103">
-        <v>62</v>
-      </c>
-      <c r="G103">
-        <v>9313</v>
-      </c>
-      <c r="H103">
-        <v>144</v>
-      </c>
-      <c r="I103">
-        <v>21</v>
+      <c r="F103" s="8">
+        <v>222</v>
+      </c>
+      <c r="G103" s="9">
+        <v>9317</v>
+      </c>
+      <c r="H103" s="10">
+        <v>304</v>
+      </c>
+      <c r="I103" s="7">
+        <v>181</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3446,17 +3457,17 @@
       <c r="E104" s="8">
         <v>232</v>
       </c>
-      <c r="F104">
-        <v>9312</v>
-      </c>
-      <c r="G104">
-        <v>103</v>
-      </c>
-      <c r="H104">
-        <v>9214</v>
-      </c>
-      <c r="I104">
-        <v>9711</v>
+      <c r="F104" s="8">
+        <v>9316</v>
+      </c>
+      <c r="G104" s="9">
+        <v>263</v>
+      </c>
+      <c r="H104" s="10">
+        <v>9218</v>
+      </c>
+      <c r="I104" s="7">
+        <v>9715</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -3475,17 +3486,17 @@
       <c r="E105" s="8">
         <v>9426</v>
       </c>
-      <c r="F105">
-        <v>9112</v>
-      </c>
-      <c r="G105">
-        <v>9113</v>
-      </c>
-      <c r="H105">
-        <v>9424</v>
-      </c>
-      <c r="I105">
-        <v>9211</v>
+      <c r="F105" s="8">
+        <v>9116</v>
+      </c>
+      <c r="G105" s="9">
+        <v>9117</v>
+      </c>
+      <c r="H105" s="10">
+        <v>9428</v>
+      </c>
+      <c r="I105" s="7">
+        <v>9215</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -3504,17 +3515,17 @@
       <c r="E106" s="8">
         <v>9216</v>
       </c>
-      <c r="F106">
-        <v>9512</v>
-      </c>
-      <c r="G106">
-        <v>92</v>
-      </c>
-      <c r="H106">
-        <v>133</v>
-      </c>
-      <c r="I106">
-        <v>9511</v>
+      <c r="F106" s="8">
+        <v>9516</v>
+      </c>
+      <c r="G106" s="9">
+        <v>252</v>
+      </c>
+      <c r="H106" s="10">
+        <v>293</v>
+      </c>
+      <c r="I106" s="7">
+        <v>9515</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -3533,17 +3544,17 @@
       <c r="E107" s="8">
         <v>243</v>
       </c>
-      <c r="F107">
-        <v>51</v>
-      </c>
-      <c r="G107">
-        <v>9123</v>
-      </c>
-      <c r="H107">
-        <v>9324</v>
-      </c>
-      <c r="I107">
-        <v>14</v>
+      <c r="F107" s="8">
+        <v>211</v>
+      </c>
+      <c r="G107" s="9">
+        <v>9127</v>
+      </c>
+      <c r="H107" s="10">
+        <v>9328</v>
+      </c>
+      <c r="I107" s="7">
+        <v>174</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -3562,17 +3573,17 @@
       <c r="E108" s="8">
         <v>9726</v>
       </c>
-      <c r="F108">
-        <v>9712</v>
-      </c>
-      <c r="G108">
-        <v>9513</v>
-      </c>
-      <c r="H108">
-        <v>9724</v>
-      </c>
-      <c r="I108">
-        <v>9111</v>
+      <c r="F108" s="8">
+        <v>9716</v>
+      </c>
+      <c r="G108" s="9">
+        <v>9517</v>
+      </c>
+      <c r="H108" s="10">
+        <v>9728</v>
+      </c>
+      <c r="I108" s="7">
+        <v>9115</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -3591,17 +3602,17 @@
       <c r="E109" s="9">
         <v>9517</v>
       </c>
-      <c r="F109">
-        <v>9411</v>
-      </c>
-      <c r="G109">
-        <v>9722</v>
-      </c>
-      <c r="H109">
-        <v>9423</v>
-      </c>
-      <c r="I109">
-        <v>9514</v>
+      <c r="F109" s="7">
+        <v>9415</v>
+      </c>
+      <c r="G109" s="8">
+        <v>9726</v>
+      </c>
+      <c r="H109" s="9">
+        <v>9427</v>
+      </c>
+      <c r="I109" s="10">
+        <v>9518</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -3620,17 +3631,17 @@
       <c r="E110" s="9">
         <v>9127</v>
       </c>
-      <c r="F110">
-        <v>9721</v>
-      </c>
-      <c r="G110">
-        <v>81</v>
-      </c>
-      <c r="H110">
-        <v>122</v>
-      </c>
-      <c r="I110">
-        <v>163</v>
+      <c r="F110" s="7">
+        <v>9725</v>
+      </c>
+      <c r="G110" s="8">
+        <v>241</v>
+      </c>
+      <c r="H110" s="9">
+        <v>282</v>
+      </c>
+      <c r="I110" s="10">
+        <v>323</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -3649,17 +3660,17 @@
       <c r="E111" s="9">
         <v>254</v>
       </c>
-      <c r="F111">
-        <v>44</v>
-      </c>
-      <c r="G111">
-        <v>9212</v>
-      </c>
-      <c r="H111">
-        <v>9723</v>
-      </c>
-      <c r="I111">
-        <v>9124</v>
+      <c r="F111" s="7">
+        <v>204</v>
+      </c>
+      <c r="G111" s="8">
+        <v>9216</v>
+      </c>
+      <c r="H111" s="9">
+        <v>9727</v>
+      </c>
+      <c r="I111" s="10">
+        <v>9128</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -3678,17 +3689,17 @@
       <c r="E112" s="9">
         <v>9117</v>
       </c>
-      <c r="F112">
-        <v>9421</v>
-      </c>
-      <c r="G112">
-        <v>9422</v>
-      </c>
-      <c r="H112">
-        <v>9213</v>
-      </c>
-      <c r="I112">
-        <v>9314</v>
+      <c r="F112" s="7">
+        <v>9425</v>
+      </c>
+      <c r="G112" s="8">
+        <v>9426</v>
+      </c>
+      <c r="H112" s="9">
+        <v>9217</v>
+      </c>
+      <c r="I112" s="10">
+        <v>9318</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -3707,17 +3718,17 @@
       <c r="E113" s="9">
         <v>261</v>
       </c>
-      <c r="F113">
-        <v>9311</v>
-      </c>
-      <c r="G113">
-        <v>74</v>
-      </c>
-      <c r="H113">
-        <v>9323</v>
-      </c>
-      <c r="I113">
-        <v>152</v>
+      <c r="F113" s="7">
+        <v>9315</v>
+      </c>
+      <c r="G113" s="8">
+        <v>234</v>
+      </c>
+      <c r="H113" s="9">
+        <v>9327</v>
+      </c>
+      <c r="I113" s="10">
+        <v>312</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -3736,17 +3747,17 @@
       <c r="E114" s="9">
         <v>9317</v>
       </c>
-      <c r="F114">
-        <v>33</v>
-      </c>
-      <c r="G114">
-        <v>9412</v>
-      </c>
-      <c r="H114">
-        <v>111</v>
-      </c>
-      <c r="I114">
-        <v>9414</v>
+      <c r="F114" s="7">
+        <v>193</v>
+      </c>
+      <c r="G114" s="8">
+        <v>9416</v>
+      </c>
+      <c r="H114" s="9">
+        <v>271</v>
+      </c>
+      <c r="I114" s="10">
+        <v>9418</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -3765,17 +3776,17 @@
       <c r="E115" s="9">
         <v>9417</v>
       </c>
-      <c r="F115">
-        <v>9121</v>
-      </c>
-      <c r="G115">
-        <v>9122</v>
-      </c>
-      <c r="H115">
-        <v>9713</v>
-      </c>
-      <c r="I115">
-        <v>9114</v>
+      <c r="F115" s="7">
+        <v>9125</v>
+      </c>
+      <c r="G115" s="8">
+        <v>9126</v>
+      </c>
+      <c r="H115" s="9">
+        <v>9717</v>
+      </c>
+      <c r="I115" s="10">
+        <v>9118</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -3794,17 +3805,17 @@
       <c r="E116" s="9">
         <v>9717</v>
       </c>
-      <c r="F116">
-        <v>9321</v>
-      </c>
-      <c r="G116">
-        <v>9322</v>
-      </c>
-      <c r="H116">
-        <v>9413</v>
-      </c>
-      <c r="I116">
-        <v>9714</v>
+      <c r="F116" s="7">
+        <v>9325</v>
+      </c>
+      <c r="G116" s="8">
+        <v>9326</v>
+      </c>
+      <c r="H116" s="9">
+        <v>9417</v>
+      </c>
+      <c r="I116" s="10">
+        <v>9718</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -3823,17 +3834,17 @@
       <c r="E117" s="9">
         <v>272</v>
       </c>
-      <c r="F117">
-        <v>22</v>
-      </c>
-      <c r="G117">
-        <v>63</v>
-      </c>
-      <c r="H117">
-        <v>9313</v>
-      </c>
-      <c r="I117">
-        <v>141</v>
+      <c r="F117" s="7">
+        <v>182</v>
+      </c>
+      <c r="G117" s="8">
+        <v>223</v>
+      </c>
+      <c r="H117" s="9">
+        <v>9317</v>
+      </c>
+      <c r="I117" s="10">
+        <v>301</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -3852,17 +3863,17 @@
       <c r="E118" s="9">
         <v>9327</v>
       </c>
-      <c r="F118">
-        <v>9711</v>
-      </c>
-      <c r="G118">
-        <v>9312</v>
-      </c>
-      <c r="H118">
-        <v>104</v>
-      </c>
-      <c r="I118">
-        <v>9214</v>
+      <c r="F118" s="7">
+        <v>9715</v>
+      </c>
+      <c r="G118" s="8">
+        <v>9316</v>
+      </c>
+      <c r="H118" s="9">
+        <v>264</v>
+      </c>
+      <c r="I118" s="10">
+        <v>9218</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -3881,17 +3892,17 @@
       <c r="E119" s="9">
         <v>9217</v>
       </c>
-      <c r="F119">
-        <v>9211</v>
-      </c>
-      <c r="G119">
-        <v>9112</v>
-      </c>
-      <c r="H119">
-        <v>9113</v>
-      </c>
-      <c r="I119">
-        <v>9424</v>
+      <c r="F119" s="7">
+        <v>9215</v>
+      </c>
+      <c r="G119" s="8">
+        <v>9116</v>
+      </c>
+      <c r="H119" s="9">
+        <v>9117</v>
+      </c>
+      <c r="I119" s="10">
+        <v>9428</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -3910,17 +3921,17 @@
       <c r="E120" s="9">
         <v>9727</v>
       </c>
-      <c r="F120">
-        <v>9511</v>
-      </c>
-      <c r="G120">
-        <v>9512</v>
-      </c>
-      <c r="H120">
-        <v>93</v>
-      </c>
-      <c r="I120">
-        <v>134</v>
+      <c r="F120" s="7">
+        <v>9515</v>
+      </c>
+      <c r="G120" s="8">
+        <v>9516</v>
+      </c>
+      <c r="H120" s="9">
+        <v>253</v>
+      </c>
+      <c r="I120" s="10">
+        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -3939,17 +3950,17 @@
       <c r="E121" s="9">
         <v>283</v>
       </c>
-      <c r="F121">
-        <v>11</v>
-      </c>
-      <c r="G121">
-        <v>52</v>
-      </c>
-      <c r="H121">
-        <v>9123</v>
-      </c>
-      <c r="I121">
-        <v>9324</v>
+      <c r="F121" s="7">
+        <v>171</v>
+      </c>
+      <c r="G121" s="8">
+        <v>212</v>
+      </c>
+      <c r="H121" s="9">
+        <v>9127</v>
+      </c>
+      <c r="I121" s="10">
+        <v>9328</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -3968,17 +3979,17 @@
       <c r="E122" s="9">
         <v>9427</v>
       </c>
-      <c r="F122">
-        <v>9111</v>
-      </c>
-      <c r="G122">
-        <v>9712</v>
-      </c>
-      <c r="H122">
-        <v>9513</v>
-      </c>
-      <c r="I122">
-        <v>9724</v>
+      <c r="F122" s="7">
+        <v>9115</v>
+      </c>
+      <c r="G122" s="8">
+        <v>9716</v>
+      </c>
+      <c r="H122" s="9">
+        <v>9517</v>
+      </c>
+      <c r="I122" s="10">
+        <v>9728</v>
       </c>
     </row>
   </sheetData>
